--- a/plan-y-cronograma/Sesiones de Teams · 36 reuniones.xlsx
+++ b/plan-y-cronograma/Sesiones de Teams · 36 reuniones.xlsx
@@ -70,10 +70,10 @@
     <t xml:space="preserve">Encuentro 1</t>
   </si>
   <si>
-    <t xml:space="preserve">16/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viernes 16 de octubre</t>
+    <t xml:space="preserve">23/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">viernes 23 de octubre</t>
   </si>
   <si>
     <t xml:space="preserve">7:30 a.m.</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">Consultorio</t>
   </si>
   <si>
-    <t xml:space="preserve">21/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miércoles 21 de octubre</t>
+    <t xml:space="preserve">28/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miércoles 28 de octubre</t>
   </si>
   <si>
     <t xml:space="preserve">4:00 p.m.</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">Encuentro 2</t>
   </si>
   <si>
-    <t xml:space="preserve">23/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viernes 23 de octubre</t>
+    <t xml:space="preserve">30/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">viernes 30 de octubre</t>
   </si>
   <si>
     <t xml:space="preserve">Super Humanos · Taller 1 · La IA no sabe nada de tu cliente (todavía) (parte 2)</t>
@@ -126,10 +126,10 @@
 Al final abrimos la evaluación del taller: diez preguntas, cinco minutos, suma 30 puntos.</t>
   </si>
   <si>
-    <t xml:space="preserve">06/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viernes 6 de noviembre</t>
+    <t xml:space="preserve">13/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">viernes 13 de noviembre</t>
   </si>
   <si>
     <t xml:space="preserve">Super Humanos · Taller 2 · Tu cartera tiene cosas que contarte</t>
@@ -139,19 +139,19 @@
 Encuentro 1 de 2. Hora y media, con la herramienta abierta. Si no puedes conectarte, la grabación queda en la plataforma al día siguiente.</t>
   </si>
   <si>
-    <t xml:space="preserve">11/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miércoles 11 de noviembre</t>
+    <t xml:space="preserve">18/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miércoles 18 de noviembre</t>
   </si>
   <si>
     <t xml:space="preserve">Super Humanos · Consultorio del Taller 2</t>
   </si>
   <si>
-    <t xml:space="preserve">13/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viernes 13 de noviembre</t>
+    <t xml:space="preserve">20/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">viernes 20 de noviembre</t>
   </si>
   <si>
     <t xml:space="preserve">Super Humanos · Taller 2 · Tu cartera tiene cosas que contarte (parte 2)</t>
@@ -284,6 +284,12 @@
     <t xml:space="preserve">Administrativo</t>
   </si>
   <si>
+    <t xml:space="preserve">21/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miércoles 21 de octubre</t>
+  </si>
+  <si>
     <t xml:space="preserve">8:00 a.m.</t>
   </si>
   <si>
@@ -297,13 +303,13 @@
 Encuentro 1 de 2. Hora y media, con la herramienta abierta. Si no puedes conectarte, la grabación queda en la plataforma al día siguiente.</t>
   </si>
   <si>
-    <t xml:space="preserve">28/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miércoles 28 de octubre</t>
-  </si>
-  <si>
     <t xml:space="preserve">Super Humanos · Taller 1 · La IA no consulta tus sistemas (todavía) (parte 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miércoles 11 de noviembre</t>
   </si>
   <si>
     <t xml:space="preserve">Super Humanos · Taller 2 · Tres días armando el reporte, cero analizándolo</t>
@@ -317,12 +323,6 @@
   </si>
   <si>
     <t xml:space="preserve">martes 17 de noviembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miércoles 18 de noviembre</t>
   </si>
   <si>
     <t xml:space="preserve">Super Humanos · Taller 2 · Tres días armando el reporte, cero analizándolo (parte 2)</t>
@@ -5834,22 +5834,22 @@
         <v>12</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5863,10 +5863,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>22</v>
@@ -5892,16 +5892,16 @@
         <v>26</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>88</v>
@@ -5921,22 +5921,22 @@
         <v>12</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5950,10 +5950,10 @@
         <v>19</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>22</v>
@@ -5979,16 +5979,16 @@
         <v>26</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>95</v>
@@ -6014,10 +6014,10 @@
         <v>97</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>98</v>
@@ -6072,10 +6072,10 @@
         <v>103</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>104</v>
@@ -6101,10 +6101,10 @@
         <v>106</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>107</v>
@@ -6159,10 +6159,10 @@
         <v>112</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>113</v>
@@ -6188,10 +6188,10 @@
         <v>66</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>114</v>
@@ -6246,10 +6246,10 @@
         <v>119</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>120</v>
@@ -6275,10 +6275,10 @@
         <v>76</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>73</v>
@@ -6333,10 +6333,10 @@
         <v>124</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>80</v>
